--- a/17 18 20/2 Tableau/6.Data Modeling/3.Relationship/Relationship.xlsx
+++ b/17 18 20/2 Tableau/6.Data Modeling/3.Relationship/Relationship.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Study\Eathans\Ethans\17 18 20\2 Tableau\5.Relationship\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Study\Eathans\Ethans\17 18 20\2 Tableau\6.Data Modeling\3.Relationship\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="7920"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="7920" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="One-Many" sheetId="1" r:id="rId1"/>
